--- a/Financial Analysis/Models (Space).xlsx
+++ b/Financial Analysis/Models (Space).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDACFFCF-8661-443E-B131-FC74B7C4A564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F090BA-A253-40DB-BD3F-E463BEDE3547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44325DD5-B9EA-4A3A-86DA-3F4C5EA9FAF1}"/>
   </bookViews>
@@ -18,6 +18,8 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
     <author>Anton</author>
   </authors>
   <commentList>
-    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{8420850D-3470-4552-9E11-112D33182E33}">
+    <comment ref="W2" authorId="0" shapeId="0" xr:uid="{8420850D-3470-4552-9E11-112D33182E33}">
       <text>
         <r>
           <rPr>
@@ -63,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Company</t>
   </si>
@@ -119,21 +121,6 @@
     <t>2028 EV/E</t>
   </si>
   <si>
-    <t>2023 Rev</t>
-  </si>
-  <si>
-    <t>2022 RevG</t>
-  </si>
-  <si>
-    <t>2023 RevG</t>
-  </si>
-  <si>
-    <t>2023 GM%</t>
-  </si>
-  <si>
-    <t>2023 OM%</t>
-  </si>
-  <si>
     <t>Discount</t>
   </si>
   <si>
@@ -173,23 +160,51 @@
     <t>LUNR US</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>ASTS US</t>
   </si>
   <si>
     <t>RKLB US</t>
+  </si>
+  <si>
+    <t>Firefly Aerospace</t>
+  </si>
+  <si>
+    <t>FLY US</t>
+  </si>
+  <si>
+    <t>2035 EV/E</t>
+  </si>
+  <si>
+    <t>2025 Rev</t>
+  </si>
+  <si>
+    <t>2024 RevG</t>
+  </si>
+  <si>
+    <t>2025 RevG</t>
+  </si>
+  <si>
+    <t>2025 GM%</t>
+  </si>
+  <si>
+    <t>2025 OM%</t>
+  </si>
+  <si>
+    <t>2025 EV/R</t>
+  </si>
+  <si>
+    <t>SPAC US</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -296,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -344,7 +359,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -377,35 +399,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>20.36</v>
+            <v>53.74</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45923</v>
           </cell>
           <cell r="G3">
-            <v>45785</v>
+            <v>45979</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>9233.26</v>
+            <v>25762.955999999998</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>77.999999999999943</v>
+            <v>332.7000000000001</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>9155.26</v>
+            <v>25430.255999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="T5">
-            <v>244.6</v>
+          <cell r="V5">
+            <v>619.1</v>
           </cell>
         </row>
         <row r="20">
@@ -416,40 +438,43 @@
             <v>-190.20000000000005</v>
           </cell>
           <cell r="V20">
-            <v>-241.2772600000001</v>
+            <v>-242.68269999999998</v>
           </cell>
           <cell r="W20">
-            <v>-266.73522480000014</v>
+            <v>-270.076752</v>
           </cell>
           <cell r="X20">
-            <v>-268.88498010000018</v>
+            <v>-283.52187765000002</v>
           </cell>
           <cell r="Y20">
-            <v>-256.02928758000007</v>
+            <v>-288.37844268749996</v>
+          </cell>
+          <cell r="AF20">
+            <v>1233.8485140251516</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="S26">
-            <v>2.3922829581993565</v>
-          </cell>
-          <cell r="T26">
-            <v>0.15924170616113731</v>
+          <cell r="U26">
+            <v>0.78372853638593609</v>
+          </cell>
+          <cell r="V26">
+            <v>0.41897776759110728</v>
           </cell>
           <cell r="AI26">
-            <v>0.09</v>
+            <v>0.08</v>
           </cell>
         </row>
         <row r="29">
-          <cell r="T29">
-            <v>0.21054783319705642</v>
+          <cell r="V29">
+            <v>0.31374575997415605</v>
           </cell>
         </row>
         <row r="32">
-          <cell r="U32">
-            <v>-0.43479257391702969</v>
+          <cell r="V32">
+            <v>-0.37737037635277015</v>
           </cell>
           <cell r="AI32">
-            <v>-0.5430347296183955</v>
+            <v>-0.72222652749219152</v>
           </cell>
         </row>
         <row r="33">
@@ -493,6 +518,156 @@
         <row r="9">
           <cell r="D9">
             <v>7139.5250000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>45.37</v>
+          </cell>
+          <cell r="E3">
+            <v>45898</v>
+          </cell>
+          <cell r="G3">
+            <v>45945</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>6578.65</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>29.300000000000011</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>6549.3499999999995</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="5">
+          <cell r="N5">
+            <v>228</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19">
+            <v>-156.30000000000001</v>
+          </cell>
+          <cell r="M19">
+            <v>-265.8</v>
+          </cell>
+          <cell r="N19">
+            <v>-367.6</v>
+          </cell>
+          <cell r="O19">
+            <v>-499.71199999999999</v>
+          </cell>
+          <cell r="P19">
+            <v>-643.84879999999998</v>
+          </cell>
+          <cell r="Q19">
+            <v>-777.07496000000003</v>
+          </cell>
+          <cell r="X19">
+            <v>1399.5137362608468</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="M25">
+            <v>0.10144927536231885</v>
+          </cell>
+          <cell r="N25">
+            <v>2.7499999999999996</v>
+          </cell>
+          <cell r="AA25">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="N26">
+            <v>0.05</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="N29">
+            <v>-1.2570175438596491</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AA31">
+            <v>-0.5860055723140617</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="AA32" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>8.77</v>
+          </cell>
+          <cell r="E3">
+            <v>45899</v>
+          </cell>
+          <cell r="G3">
+            <v>45973</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>1567.1989999999998</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>344.9</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>1222.299</v>
           </cell>
         </row>
       </sheetData>
@@ -799,32 +974,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496816B-CF00-47B4-9B9E-E5812753DAD8}">
-  <dimension ref="B2:AF7"/>
+  <dimension ref="B2:AH8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="16.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="11" customWidth="1"/>
+    <col min="4" max="7" width="8.88671875" style="1" customWidth="1"/>
     <col min="8" max="13" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="19" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.88671875" style="1"/>
-    <col min="31" max="31" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="1"/>
+    <col min="20" max="20" width="9.5546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.88671875" style="1"/>
+    <col min="33" max="33" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -879,47 +1053,53 @@
       <c r="S2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AH2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" s="3" t="s">
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -933,8 +1113,8 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="7">
-        <f t="shared" ref="N3:S3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
-        <v>-50.1383351588171</v>
+        <f t="shared" ref="N3:S3" si="0">TRIMMEAN(N5:N1048576,80%)</f>
+        <v>-90.584994362373592</v>
       </c>
       <c r="O3" s="7" t="e">
         <f t="shared" si="0"/>
@@ -956,184 +1136,337 @@
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="T3" s="8"/>
-      <c r="U3" s="9">
-        <f t="shared" ref="U3:Z3" si="1">TRIMMEAN(U4:U1048576,80%)</f>
-        <v>2.3922829581993565</v>
-      </c>
-      <c r="V3" s="9">
-        <f t="shared" si="1"/>
-        <v>0.15924170616113731</v>
+      <c r="T3" s="7"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="22">
+        <f>TRIMMEAN(V4:V1048524,80%)</f>
+        <v>28.725219298245612</v>
       </c>
       <c r="W3" s="9">
-        <f t="shared" si="1"/>
-        <v>0.21054783319705642</v>
+        <f t="shared" ref="W3:AB3" si="1">TRIMMEAN(W5:W1048576,80%)</f>
+        <v>0.44258890587412747</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" si="1"/>
-        <v>-0.43479257391702969</v>
+        <v>1.5844888837955535</v>
       </c>
       <c r="Y3" s="9">
         <f t="shared" si="1"/>
-        <v>0.09</v>
+        <v>0.18187287998707802</v>
       </c>
       <c r="Z3" s="9">
         <f t="shared" si="1"/>
-        <v>-0.5430347296183955</v>
-      </c>
-      <c r="AA3" s="10" t="e">
-        <f>INDEX(AA4:AA53,MODE(MATCH(AA4:AA53,AA4:AA53,0)))</f>
+        <v>-0.8171939601062097</v>
+      </c>
+      <c r="AA3" s="9">
+        <f t="shared" si="1"/>
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="AB3" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.65411604990312666</v>
+      </c>
+      <c r="AC3" s="10" t="e">
+        <f>INDEX(AC5:AC53,MODE(MATCH(AC5:AC53,AC5:AC53,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="11"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="11"/>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
-        <v>31</v>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="12">
+        <v>42</v>
+      </c>
+      <c r="G4" s="13">
+        <v>400000</v>
+      </c>
+      <c r="U4" s="15">
+        <v>15500</v>
+      </c>
+      <c r="V4" s="19">
+        <f>G4/U4</f>
+        <v>25.806451612903224</v>
+      </c>
+      <c r="AG4" s="21">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="12">
         <f>[1]Main!$D$3</f>
-        <v>20.36</v>
-      </c>
-      <c r="E4" s="13">
+        <v>53.74</v>
+      </c>
+      <c r="E5" s="13">
         <f>[1]Main!$D$5</f>
-        <v>9233.26</v>
-      </c>
-      <c r="F4" s="13">
+        <v>25762.955999999998</v>
+      </c>
+      <c r="F5" s="13">
         <f>[1]Main!$D$8</f>
-        <v>77.999999999999943</v>
-      </c>
-      <c r="G4" s="13">
+        <v>332.7000000000001</v>
+      </c>
+      <c r="G5" s="13">
         <f>[1]Main!$D$9</f>
-        <v>9155.26</v>
-      </c>
-      <c r="H4" s="13">
+        <v>25430.255999999998</v>
+      </c>
+      <c r="H5" s="13">
         <f>[1]Model!T$20</f>
         <v>-182.59999999999997</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I5" s="13">
         <f>[1]Model!U$20</f>
         <v>-190.20000000000005</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J5" s="13">
         <f>[1]Model!V$20</f>
-        <v>-241.2772600000001</v>
-      </c>
-      <c r="K4" s="13">
+        <v>-242.68269999999998</v>
+      </c>
+      <c r="K5" s="13">
         <f>[1]Model!W$20</f>
-        <v>-266.73522480000014</v>
-      </c>
-      <c r="L4" s="13">
+        <v>-270.076752</v>
+      </c>
+      <c r="L5" s="13">
         <f>[1]Model!X$20</f>
-        <v>-268.88498010000018</v>
-      </c>
-      <c r="M4" s="13">
+        <v>-283.52187765000002</v>
+      </c>
+      <c r="M5" s="13">
         <f>[1]Model!Y$20</f>
-        <v>-256.02928758000007</v>
-      </c>
-      <c r="N4" s="14">
-        <f t="shared" ref="N4" si="2">$G4/H4</f>
-        <v>-50.1383351588171</v>
-      </c>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="15">
-        <f>[1]Model!$T$5</f>
-        <v>244.6</v>
-      </c>
-      <c r="U4" s="16">
-        <f>[1]Model!S$26</f>
-        <v>2.3922829581993565</v>
-      </c>
-      <c r="V4" s="16">
-        <f>[1]Model!T$26</f>
-        <v>0.15924170616113731</v>
-      </c>
-      <c r="W4" s="16">
-        <f>[1]Model!$T$29</f>
-        <v>0.21054783319705642</v>
-      </c>
-      <c r="X4" s="16">
-        <f>[1]Model!$U$32</f>
-        <v>-0.43479257391702969</v>
-      </c>
-      <c r="Y4" s="16">
+        <v>-288.37844268749996</v>
+      </c>
+      <c r="N5" s="14">
+        <f t="shared" ref="N5" si="2">$G5/H5</f>
+        <v>-139.26755750273824</v>
+      </c>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14">
+        <f>G5/[1]Model!$AF$20</f>
+        <v>20.61051718337735</v>
+      </c>
+      <c r="U5" s="15">
+        <f>[1]Model!$V$5</f>
+        <v>619.1</v>
+      </c>
+      <c r="V5" s="19">
+        <f>G5/U5</f>
+        <v>41.07616863188499</v>
+      </c>
+      <c r="W5" s="16">
+        <f>[1]Model!U$26</f>
+        <v>0.78372853638593609</v>
+      </c>
+      <c r="X5" s="16">
+        <f>[1]Model!V$26</f>
+        <v>0.41897776759110728</v>
+      </c>
+      <c r="Y5" s="16">
+        <f>[1]Model!$V$29</f>
+        <v>0.31374575997415605</v>
+      </c>
+      <c r="Z5" s="16">
+        <f>[1]Model!$V$32</f>
+        <v>-0.37737037635277015</v>
+      </c>
+      <c r="AA5" s="16">
         <f>[1]Model!$AI$26</f>
-        <v>0.09</v>
-      </c>
-      <c r="Z4" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="AB5" s="16">
         <f>[1]Model!$AI$32</f>
-        <v>-0.5430347296183955</v>
-      </c>
-      <c r="AA4" s="16" t="str">
+        <v>-0.72222652749219152</v>
+      </c>
+      <c r="AC5" s="16" t="str">
         <f>[1]Model!$AI$33</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="11"/>
-      <c r="AE4" s="17">
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="11"/>
+      <c r="AG5" s="17">
         <f>[1]Main!$E$3</f>
-        <v>45771</v>
-      </c>
-      <c r="AF4" s="17">
+        <v>45923</v>
+      </c>
+      <c r="AH5" s="17">
         <f>[1]Main!$G$3</f>
-        <v>45785</v>
+        <v>45979</v>
       </c>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B5" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="12">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="12">
         <f>[2]Main!$D$3</f>
         <v>23.85</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E6" s="13">
         <f>[2]Main!$D$5</f>
         <v>7548.5250000000005</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F6" s="13">
         <f>[2]Main!$D$8</f>
         <v>409</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G6" s="13">
         <f>[2]Main!$D$9</f>
         <v>7139.5250000000005</v>
       </c>
+      <c r="V6" s="20"/>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>36</v>
+      <c r="C7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="12">
+        <f>[3]Main!$D$3</f>
+        <v>45.37</v>
+      </c>
+      <c r="E7" s="13">
+        <f>[3]Main!$D$5</f>
+        <v>6578.65</v>
+      </c>
+      <c r="F7" s="13">
+        <f>[3]Main!$D$8</f>
+        <v>29.300000000000011</v>
+      </c>
+      <c r="G7" s="13">
+        <f>[3]Main!$D$9</f>
+        <v>6549.3499999999995</v>
+      </c>
+      <c r="H7" s="13">
+        <f>[3]Model!L$19</f>
+        <v>-156.30000000000001</v>
+      </c>
+      <c r="I7" s="13">
+        <f>[3]Model!M$19</f>
+        <v>-265.8</v>
+      </c>
+      <c r="J7" s="13">
+        <f>[3]Model!N$19</f>
+        <v>-367.6</v>
+      </c>
+      <c r="K7" s="13">
+        <f>[3]Model!O$19</f>
+        <v>-499.71199999999999</v>
+      </c>
+      <c r="L7" s="13">
+        <f>[3]Model!P$19</f>
+        <v>-643.84879999999998</v>
+      </c>
+      <c r="M7" s="13">
+        <f>[3]Model!Q$19</f>
+        <v>-777.07496000000003</v>
+      </c>
+      <c r="N7" s="14">
+        <f>$G7/H7</f>
+        <v>-41.90243122200895</v>
+      </c>
+      <c r="T7" s="14">
+        <f>G7/[3]Model!$X$19</f>
+        <v>4.6797325601806783</v>
+      </c>
+      <c r="U7" s="15">
+        <f>[3]Model!$N$5</f>
+        <v>228</v>
+      </c>
+      <c r="V7" s="19">
+        <f>G7/U7</f>
+        <v>28.725219298245612</v>
+      </c>
+      <c r="W7" s="16">
+        <f>[3]Model!M$25</f>
+        <v>0.10144927536231885</v>
+      </c>
+      <c r="X7" s="16">
+        <f>[3]Model!N$25</f>
+        <v>2.7499999999999996</v>
+      </c>
+      <c r="Y7" s="16">
+        <f>[3]Model!$N$26</f>
+        <v>0.05</v>
+      </c>
+      <c r="Z7" s="16">
+        <f>[3]Model!$N$29</f>
+        <v>-1.2570175438596491</v>
+      </c>
+      <c r="AA7" s="16">
+        <f>[3]Model!$AA$25</f>
+        <v>0.09</v>
+      </c>
+      <c r="AB7" s="16">
+        <f>[3]Model!$AA$31</f>
+        <v>-0.5860055723140617</v>
+      </c>
+      <c r="AC7" s="11" t="str">
+        <f>[3]Model!$AA$32</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AG7" s="17">
+        <f>[3]Main!$E$3</f>
+        <v>45898</v>
+      </c>
+      <c r="AH7" s="17">
+        <f>[3]Main!$G$3</f>
+        <v>45945</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>35</v>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="12">
+        <f>[4]Main!$D$3</f>
+        <v>8.77</v>
+      </c>
+      <c r="E8" s="13">
+        <f>[4]Main!$D$5</f>
+        <v>1567.1989999999998</v>
+      </c>
+      <c r="F8" s="13">
+        <f>[4]Main!$D$8</f>
+        <v>344.9</v>
+      </c>
+      <c r="G8" s="13">
+        <f>[4]Main!$D$9</f>
+        <v>1222.299</v>
+      </c>
+      <c r="AG8" s="17">
+        <f>[4]Main!$E$3</f>
+        <v>45899</v>
+      </c>
+      <c r="AH8" s="17">
+        <f>[4]Main!$G$3</f>
+        <v>45973</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{BCD3688A-357B-484F-990F-C8AA1C66B280}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{8B65215F-AFA0-4639-AADC-CE4AF968375D}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{BCD3688A-357B-484F-990F-C8AA1C66B280}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{8B65215F-AFA0-4639-AADC-CE4AF968375D}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{D940230D-C614-4CEB-8774-12CC00908CB1}"/>
+    <hyperlink ref="B8" r:id="rId4" xr:uid="{03376952-0DCA-4D2B-AEA3-EC494F2D5995}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>